--- a/public/assets/data/projects.xlsx
+++ b/public/assets/data/projects.xlsx
@@ -1,41 +1,179 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ragha\OneDrive\Documents\Raghav Personal\portfolio\public\assets\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16D4E113-4B14-489D-BFA0-7F73E173B824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Projects" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="49">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>tech</t>
+  </si>
+  <si>
+    <t>github</t>
+  </si>
+  <si>
+    <t>demo</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>progress</t>
+  </si>
+  <si>
+    <t>featured</t>
+  </si>
+  <si>
+    <t>Jarvis</t>
+  </si>
+  <si>
+    <t>A desktop voice / text assistant that listens to commands and performs tasks like opening apps, fetching data, etc.</t>
+  </si>
+  <si>
+    <t>Python, Eel, HTML, JavaScript</t>
+  </si>
+  <si>
+    <t>https://github.com/RaghavSethi006/jarvis</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Bank Management System</t>
+  </si>
+  <si>
+    <t>A system to manage bank operations including account creation, fund transfers, and transaction tracking.</t>
+  </si>
+  <si>
+    <t>(specify language / DB)</t>
+  </si>
+  <si>
+    <t>https://github.com/RaghavSethi006/bank-management-system</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>RAG-based Chatbot for Embedded Data</t>
+  </si>
+  <si>
+    <t>A chatbot using Retrieval-Augmented Generation (RAG) that retrieves domain-specific embedding data and responds accordingly.</t>
+  </si>
+  <si>
+    <t>(your stack, e.g. Python, LangChain, embeddings, vector DB)</t>
+  </si>
+  <si>
+    <t>https://github.com/RaghavSethi006/RAG-based-chatbot-for-custom-data-embedding</t>
+  </si>
+  <si>
+    <t>Face Recognition Attendance System</t>
+  </si>
+  <si>
+    <t>Attendance system that uses face recognition (via camera) to mark presence/absence automatically.</t>
+  </si>
+  <si>
+    <t>(e.g. Python, OpenCV, face-recognition)</t>
+  </si>
+  <si>
+    <t>https://github.com/RaghavSethi006/Face-Recognition-attendance-system-</t>
+  </si>
+  <si>
+    <t>Wi-Fi Password Extractor</t>
+  </si>
+  <si>
+    <t>A tool to extract saved Wi-Fi passwords from the system.</t>
+  </si>
+  <si>
+    <t>(specify language)</t>
+  </si>
+  <si>
+    <t>https://github.com/RaghavSethi006/Wi-Fi-password-extractor-</t>
+  </si>
+  <si>
+    <t>Travel Data Analysis App</t>
+  </si>
+  <si>
+    <t>App for analyzing travel-related data (e.g. trends, patterns, visualizations).</t>
+  </si>
+  <si>
+    <t>(your stack, e.g. Python, JS, D3, Pandas)</t>
+  </si>
+  <si>
+    <t>https://github.com/RaghavSethi006/Travel-data-analysis-app</t>
+  </si>
+  <si>
+    <t>Clock Frontend Practice</t>
+  </si>
+  <si>
+    <t>A frontend exercise / component: a clock (analog or digital) as a UI piece.</t>
+  </si>
+  <si>
+    <t>(React / Vanilla JS / CSS)</t>
+  </si>
+  <si>
+    <t>https://github.com/RaghavSethi006/Clock-frontend-practice</t>
+  </si>
+  <si>
+    <t>Rivalry Chess</t>
+  </si>
+  <si>
+    <t>A chess game / platform or UI for playing chess (possibly with opponent support).</t>
+  </si>
+  <si>
+    <t>(JS / game engine / backend stack)</t>
+  </si>
+  <si>
+    <t>https://github.github.com/RaghavSethi006/Rivalry-chess-</t>
+  </si>
+  <si>
+    <t>Smart Desk</t>
+  </si>
+  <si>
+    <t>A “smart desk” project (automated / IoT / interactive desk) — details in repository.</t>
+  </si>
+  <si>
+    <t>(whatever hardware / software stack)</t>
+  </si>
+  <si>
+    <t>https://github.com/RaghavSethi006/Smart-Desk</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +203,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,275 +542,284 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="37.09765625" customWidth="1"/>
+    <col min="3" max="3" width="111.796875" customWidth="1"/>
+    <col min="4" max="4" width="55.09765625" customWidth="1"/>
+    <col min="5" max="5" width="73.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.09765625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>title</v>
-      </c>
-      <c r="C1" t="str">
-        <v>description</v>
-      </c>
-      <c r="D1" t="str">
-        <v>tech</v>
-      </c>
-      <c r="E1" t="str">
-        <v>github</v>
-      </c>
-      <c r="F1" t="str">
-        <v>demo</v>
-      </c>
-      <c r="G1" t="str">
-        <v>status</v>
-      </c>
-      <c r="H1" t="str">
-        <v>progress</v>
-      </c>
-      <c r="I1" t="str">
-        <v>featured</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>Jarvis</v>
-      </c>
-      <c r="C2" t="str">
-        <v>A desktop voice / text assistant that listens to commands and performs tasks like opening apps, fetching data, etc.</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Python, Eel, HTML, JavaScript</v>
-      </c>
-      <c r="E2" t="str">
-        <v>https://github.com/RaghavSethi006/jarvis</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Completed</v>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
       </c>
       <c r="H2">
         <v>100</v>
       </c>
-      <c r="I2" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>Bank Management System</v>
-      </c>
-      <c r="C3" t="str">
-        <v>A system to manage bank operations including account creation, fund transfers, and transaction tracking.</v>
-      </c>
-      <c r="D3" t="str">
-        <v>(specify language / DB)</v>
-      </c>
-      <c r="E3" t="str">
-        <v>https://github.com/RaghavSethi006/bank-management-system</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Completed</v>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
       </c>
       <c r="H3">
         <v>100</v>
       </c>
-      <c r="I3" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>RAG-based Chatbot for Embedded Data</v>
-      </c>
-      <c r="C4" t="str">
-        <v>A chatbot using Retrieval-Augmented Generation (RAG) that retrieves domain-specific embedding data and responds accordingly.</v>
-      </c>
-      <c r="D4" t="str">
-        <v>(your stack, e.g. Python, LangChain, embeddings, vector DB)</v>
-      </c>
-      <c r="E4" t="str">
-        <v>https://github.com/RaghavSethi006/RAG-based-chatbot-for-custom-data-embedding</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Completed</v>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
       </c>
       <c r="H4">
         <v>100</v>
       </c>
-      <c r="I4" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="I4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v>Face Recognition Attendance System</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Attendance system that uses face recognition (via camera) to mark presence/absence automatically.</v>
-      </c>
-      <c r="D5" t="str">
-        <v>(e.g. Python, OpenCV, face-recognition)</v>
-      </c>
-      <c r="E5" t="str">
-        <v>https://github.com/RaghavSethi006/Face-Recognition-attendance-system-</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Completed</v>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
       </c>
       <c r="H5">
         <v>100</v>
       </c>
-      <c r="I5" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="I5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="str">
-        <v>Wi-Fi Password Extractor</v>
-      </c>
-      <c r="C6" t="str">
-        <v>A tool to extract saved Wi-Fi passwords from the system.</v>
-      </c>
-      <c r="D6" t="str">
-        <v>(specify language)</v>
-      </c>
-      <c r="E6" t="str">
-        <v>https://github.com/RaghavSethi006/Wi-Fi-password-extractor-</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Completed</v>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
       </c>
       <c r="H6">
         <v>100</v>
       </c>
-      <c r="I6" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="I6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="str">
-        <v>Travel Data Analysis App</v>
-      </c>
-      <c r="C7" t="str">
-        <v>App for analyzing travel-related data (e.g. trends, patterns, visualizations).</v>
-      </c>
-      <c r="D7" t="str">
-        <v>(your stack, e.g. Python, JS, D3, Pandas)</v>
-      </c>
-      <c r="E7" t="str">
-        <v>https://github.com/RaghavSethi006/Travel-data-analysis-app</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Completed</v>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
       </c>
       <c r="H7">
         <v>100</v>
       </c>
-      <c r="I7" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="I7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="str">
-        <v>Clock Frontend Practice</v>
-      </c>
-      <c r="C8" t="str">
-        <v>A frontend exercise / component: a clock (analog or digital) as a UI piece.</v>
-      </c>
-      <c r="D8" t="str">
-        <v>(React / Vanilla JS / CSS)</v>
-      </c>
-      <c r="E8" t="str">
-        <v>https://github.com/RaghavSethi006/Clock-frontend-practice</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Completed</v>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
       </c>
       <c r="H8">
         <v>100</v>
       </c>
-      <c r="I8" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="I8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="str">
-        <v>Rivalry Chess</v>
-      </c>
-      <c r="C9" t="str">
-        <v>A chess game / platform or UI for playing chess (possibly with opponent support).</v>
-      </c>
-      <c r="D9" t="str">
-        <v>(JS / game engine / backend stack)</v>
-      </c>
-      <c r="E9" t="str">
-        <v>https://github.github.com/RaghavSethi006/Rivalry-chess-</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Completed</v>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
       </c>
       <c r="H9">
         <v>100</v>
       </c>
-      <c r="I9" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="I9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="str">
-        <v>Smart Desk</v>
-      </c>
-      <c r="C10" t="str">
-        <v>A “smart desk” project (automated / IoT / interactive desk) — details in repository.</v>
-      </c>
-      <c r="D10" t="str">
-        <v>(whatever hardware / software stack)</v>
-      </c>
-      <c r="E10" t="str">
-        <v>https://github.com/RaghavSethi006/Smart-Desk</v>
-      </c>
-      <c r="G10" t="str">
-        <v>In Progress</v>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" t="s">
+        <v>48</v>
       </c>
       <c r="H10">
         <v>60</v>
       </c>
-      <c r="I10" t="str">
-        <v>No</v>
+      <c r="I10" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I10"/>
+    <ignoredError sqref="A2:I10 B1:I1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/assets/data/projects.xlsx
+++ b/public/assets/data/projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ragha\OneDrive\Documents\Raghav Personal\portfolio\public\assets\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ragha\OneDrive\Documents\Raghav Personal\My Projects\portfolio\public\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16D4E113-4B14-489D-BFA0-7F73E173B824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E942BF0-A443-4D0B-903E-130CDC5A0EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,9 +73,6 @@
     <t>A system to manage bank operations including account creation, fund transfers, and transaction tracking.</t>
   </si>
   <si>
-    <t>(specify language / DB)</t>
-  </si>
-  <si>
     <t>https://github.com/RaghavSethi006/bank-management-system</t>
   </si>
   <si>
@@ -88,9 +85,6 @@
     <t>A chatbot using Retrieval-Augmented Generation (RAG) that retrieves domain-specific embedding data and responds accordingly.</t>
   </si>
   <si>
-    <t>(your stack, e.g. Python, LangChain, embeddings, vector DB)</t>
-  </si>
-  <si>
     <t>https://github.com/RaghavSethi006/RAG-based-chatbot-for-custom-data-embedding</t>
   </si>
   <si>
@@ -100,9 +94,6 @@
     <t>Attendance system that uses face recognition (via camera) to mark presence/absence automatically.</t>
   </si>
   <si>
-    <t>(e.g. Python, OpenCV, face-recognition)</t>
-  </si>
-  <si>
     <t>https://github.com/RaghavSethi006/Face-Recognition-attendance-system-</t>
   </si>
   <si>
@@ -167,6 +158,15 @@
   </si>
   <si>
     <t>In Progress</t>
+  </si>
+  <si>
+    <t>(Python, LangChain, embeddings, vector DB)</t>
+  </si>
+  <si>
+    <t>(Python, OpenCV, face-recognition)</t>
+  </si>
+  <si>
+    <t>(Python , CSV, tkinter)</t>
   </si>
 </sst>
 </file>
@@ -544,7 +544,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="37.09765625" customWidth="1"/>
     <col min="3" max="3" width="111.796875" customWidth="1"/>
@@ -553,7 +553,7 @@
     <col min="7" max="7" width="10.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -582,7 +582,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -608,7 +608,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -619,10 +619,10 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" t="s">
         <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -631,24 +631,24 @@
         <v>100</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" t="s">
         <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -660,21 +660,21 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" t="s">
         <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>27</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -683,24 +683,24 @@
         <v>100</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
         <v>28</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" t="s">
-        <v>31</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -709,24 +709,24 @@
         <v>100</v>
       </c>
       <c r="I6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="s">
         <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" t="s">
-        <v>35</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -735,24 +735,24 @@
         <v>100</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
         <v>36</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" t="s">
-        <v>39</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -761,24 +761,24 @@
         <v>100</v>
       </c>
       <c r="I8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" t="s">
         <v>40</v>
-      </c>
-      <c r="C9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" t="s">
-        <v>43</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -787,39 +787,39 @@
         <v>100</v>
       </c>
       <c r="I9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
         <v>44</v>
       </c>
-      <c r="C10" t="s">
+      <c r="G10" t="s">
         <v>45</v>
-      </c>
-      <c r="D10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" t="s">
-        <v>48</v>
       </c>
       <c r="H10">
         <v>60</v>
       </c>
       <c r="I10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:I10 B1:I1" numberStoredAsText="1"/>
+    <ignoredError sqref="A2:I2 B1:I1 A6:I10 A4:C4 E4:I4 A5:C5 E5:I5 A3:C3 E3:I3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>